--- a/container-workshop/procurement/Container-Workshop_BOM_RevC.xlsx
+++ b/container-workshop/procurement/Container-Workshop_BOM_RevC.xlsx
@@ -71,13 +71,13 @@
     <t xml:space="preserve">Issued</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28</t>
+    <t xml:space="preserve">2026-09-24</t>
   </si>
   <si>
     <t xml:space="preserve">Quotations due</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25</t>
+    <t xml:space="preserve">2026-10-22</t>
   </si>
   <si>
     <t xml:space="preserve">Buyer contact</t>
